--- a/data/describe/few_shot/cluster/messages_foot.xlsx
+++ b/data/describe/few_shot/cluster/messages_foot.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\input_cluster\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\cluster\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B82F796-04EE-4D19-A6FE-ED7F5AEE4BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A7F34B-2165-4E05-A1B6-002E398E4B83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34950" yWindow="570" windowWidth="34065" windowHeight="17070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="51855" yWindow="2955" windowWidth="20190" windowHeight="17070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>User</t>
   </si>
@@ -45,23 +45,6 @@
     <t>A creative maestro is a player who constantly delivers dangerous passes in the attacking third, always finding space to receive the ball in crucial attacking positions, and threading ingenious smart passes while making crucial key passes. These players are also very strong in winning ground duels, demonstrating their ability to both create opportunities and fight for possession.</t>
   </si>
   <si>
-    <t xml:space="preserve">Now your task is to provide a description of a cluster.
-You will receive information about the cluster based on the latent factors that best describe it.
-For each cluster, write a concise summary based on the available information.
-The first sentence should give an overview of the cluster. 
-The second sentence should describe the cluster’s specific strengths based on the available information.
-The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
-I will provided you with the cluster description and you will return the summary. </t>
-  </si>
-  <si>
-    <t>Understood. Please provide the cluster descriptions.</t>
-  </si>
-  <si>
-    <t>This cluster describes players who are exceptionally strong goal producers, while being average in their aerial abilities.
-Their primary strength lies in their prolific goal-scoring capability and consistent ability to generate high-quality scoring chances, regardless of playing time.
-A potential weakness is their average performance in aerial duels, meaning they are not particularly dominant when the ball is contested high in the air.</t>
-  </si>
-  <si>
     <t>What does it mean when a football player is described as goal-shy?</t>
   </si>
   <si>
@@ -72,29 +55,6 @@
   </si>
   <si>
     <t>A prolific scorer is a player who truly knows how to find the back of the net, consistently delivering a high volume of goals per 90 minutes, even when we strip away penalties. These players also tend to enjoy significant time on the field, which gives them ample opportunity to showcase their exceptional scoring ability.</t>
-  </si>
-  <si>
-    <t>This cluster describes players who are prolific and consistent goal-scorers, although they exhibit a slight weakness in winning aerial duels.
-Their primary strength lies in their exceptional goal-scoring ability, consistently finding the back of the net and making every minute on the pitch count for scoring opportunities.
-However, they exhibit a slight weakness in aerial duels, meaning they are less likely to win contested balls in the air and may not be a significant threat from crosses or set pieces.</t>
-  </si>
-  <si>
-    <t>This cluster describes players who are generally not dominant in aerial duels and exhibit an average tendency to be goal-shy.
-Based on the provided factors, this cluster does not exhibit specific strengths in goal contribution or aerial ability.
-Their clear weaknesses include a marked inability to win aerial duels and a consistent lack of prolific scoring, meaning they are less impactful in situations requiring heading or regular goal production.</t>
-  </si>
-  <si>
-    <t>This cluster describes players who are exceptionally skilled at orchestrating attacks and creating chances, while maintaining a reliable, albeit not extraordinary, goal-scoring presence.
-Their paramount strength lies in their extraordinary capacity as a creative maestro, consistently dazzling with incisive passes, unlocking defenses, and winning crucial ground duels to drive their team's attack.
-However, while their goal-scoring is consistent, it remains at a normal level, indicating they are not exceptionally prolific in front of goal, especially when compared to their elite playmaking abilities.</t>
-  </si>
-  <si>
-    <t>This cluster represents players who are strong contributors to their team's attack, blending solid creative playmaking with a notable inclination to find the back of the net.
-Their specific strengths lie in their above-average ability to deliver dangerous passes, find crucial attacking space, and win ground duels, alongside a clear tendency to score goals and gain significant playing time.
-While highly effective, their creativity, though strong, doesn't reach the absolute pinnacle of a "maestro," suggesting they are consistently good but perhaps not always the most ingenious in every attacking phase.</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical football player in that cluster: ```Members of this cluster can be described as:  slightly low on good in air,  very low on goal-shy´´´</t>
   </si>
   <si>
     <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical football player in that cluster:```Members of this cluster can be described as:  normal on good in air,  quite high on prolific scorer´´´</t>
@@ -115,6 +75,44 @@
 The second sentence should describe the cluster’s specific strengths based on the available information.
 The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
 Now do the same thing with the following: ```Members of this cluster can be described as:  slightly high on creative maestro,  slightly low on goal-shy´´´</t>
+  </si>
+  <si>
+    <t>Thats really good. You truly understand the factors and names. 
+Now your task is to provide a description of a cluster.
+Please use the statistical description enclosed with ``` ´´´ . It provides information about the cluster based on the latent factors that most accurately describe it.
+Now your task is to provide a description of a cluster.
+You will receive information about the cluster based on the latent factors that best describe it.
+For each cluster, write a concise summary based on the available information.
+The first sentence should give an overview of the cluster. 
+The second sentence should describe the cluster’s specific strengths based on the available information.
+The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
+I will provided you with the cluster description and you will return the summary. 
+Here is the cluster description based on the factor scores at the cluster center, representing a typical football player in that cluster: ```Members of this cluster can be described as:  slightly low on good in air,  very low on goal-shy´´´</t>
+  </si>
+  <si>
+    <t>This cluster describes players who are prolific and consistent goal-scorers, although they exhibit a slight weakness in winning aerial duels.
+Their primary strength lies in their exceptional goal-scoring ability, consistently finding the back of the net and making every minute on the pitch count for scoring opportunities.
+However, they exhibit a slight weakness in aerial duels, meaning they are less likely to win contested balls in the air and may not be a significant threat from crosses or set pieces.</t>
+  </si>
+  <si>
+    <t>This cluster describes players who are exceptionally strong goal producers, while being average in their aerial abilities.
+Their primary strength lies in their prolific goal-scoring capability and consistent ability to generate high-quality scoring chances, regardless of playing time.
+A potential weakness is their average performance in aerial duels, meaning they are not particularly dominant when the ball is contested high in the air.</t>
+  </si>
+  <si>
+    <t>This cluster describes players who are generally not dominant in aerial duels and exhibit an average tendency to be goal-shy.
+Based on the provided factors, this cluster does not exhibit specific strengths in goal contribution or aerial ability.
+Their clear weaknesses include a marked inability to win aerial duels and a consistent lack of prolific scoring, meaning they are less impactful in situations requiring heading or regular goal production.</t>
+  </si>
+  <si>
+    <t>This cluster describes players who are exceptionally skilled at orchestrating attacks and creating chances, while maintaining a reliable, albeit not extraordinary, goal-scoring presence.
+Their paramount strength lies in their extraordinary capacity as a creative maestro, consistently dazzling with incisive passes, unlocking defenses, and winning crucial ground duels to drive their team's attack.
+However, while their goal-scoring is consistent, it remains at a normal level, indicating they are not exceptionally prolific in front of goal, especially when compared to their elite playmaking abilities.</t>
+  </si>
+  <si>
+    <t>This cluster represents players who are strong contributors to their team's attack, blending solid creative playmaking with a notable inclination to find the back of the net.
+Their specific strengths lie in their above-average ability to deliver dangerous passes, find crucial attacking space, and win ground duels, alongside a clear tendency to score goals and gain significant playing time.
+While highly effective, their creativity, though strong, doesn't reach the absolute pinnacle of a "maestro," suggesting they are consistently good but perhaps not always the most ingenious in every attacking phase.</t>
   </si>
 </sst>
 </file>
@@ -483,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="94.26953125" style="2" customWidth="1"/>
@@ -516,66 +514,58 @@
     </row>
     <row r="4" spans="1:2" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="58" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="87" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="116" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="116" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+      <c r="B7" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="116" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/data/describe/few_shot/cluster/messages_foot.xlsx
+++ b/data/describe/few_shot/cluster/messages_foot.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\cluster\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A7F34B-2165-4E05-A1B6-002E398E4B83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{262B2E6A-87A5-40BC-B8A5-340B5C5C2322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51855" yWindow="2955" windowWidth="20190" windowHeight="17070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29685" yWindow="1560" windowWidth="22560" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -45,36 +45,16 @@
     <t>A creative maestro is a player who constantly delivers dangerous passes in the attacking third, always finding space to receive the ball in crucial attacking positions, and threading ingenious smart passes while making crucial key passes. These players are also very strong in winning ground duels, demonstrating their ability to both create opportunities and fight for possession.</t>
   </si>
   <si>
-    <t>What does it mean when a football player is described as goal-shy?</t>
-  </si>
-  <si>
-    <t>What does it mean when a football player is described as prolific scorer?</t>
-  </si>
-  <si>
-    <t>When a football player is described as goal-shy, it means they aren't consistently finding the back of the net, nor are they typically expected to score much based on their play per 90 minutes. You also won't see them on the pitch for extended periods, making those scoring opportunities even rarer.</t>
-  </si>
-  <si>
-    <t>A prolific scorer is a player who truly knows how to find the back of the net, consistently delivering a high volume of goals per 90 minutes, even when we strip away penalties. These players also tend to enjoy significant time on the field, which gives them ample opportunity to showcase their exceptional scoring ability.</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical football player in that cluster:```Members of this cluster can be described as:  normal on good in air,  quite high on prolific scorer´´´</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical football player in that cluster:```Members of this cluster can be described as:  relatively low on good in air,  normal on goal-shy´´´</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical football player in that cluster:```Members of this cluster can be described as:  extremely high on creative maestro,  normal on prolific scorer´´´</t>
-  </si>
-  <si>
-    <t>Those were really good. Exactly what I am looking for. 
-Make sure you continue to use the same format and style in the next example. 
-I am now going to give you one last description task to complete. 
-You will receive information about the cluster based on the latent factors that best describe it.
-For each cluster, write a concise summary based on the available information.
-The first sentence should give an overview of the cluster. 
-The second sentence should describe the cluster’s specific strengths based on the available information.
-The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
-Now do the same thing with the following: ```Members of this cluster can be described as:  slightly high on creative maestro,  slightly low on goal-shy´´´</t>
+    <t>What does it mean when a football player is described as no scoring threat?</t>
+  </si>
+  <si>
+    <t>When a football player is described as "no scoring threat," it means they don't often find the back of the net or create many dangerous opportunities in front of goal. This also suggests they typically don't play extensive minutes on the field.</t>
+  </si>
+  <si>
+    <t>What does it mean when a football player is described as scoring threat?</t>
+  </si>
+  <si>
+    <t>A football player described as a 'scoring threat' is a true goal-getter, consistently finding the back of the net and posing a serious danger for non-penalty scoring opportunities. Their ability to score makes them a formidable presence on the field, and they don't necessarily need to play a full match to make an impact.</t>
   </si>
   <si>
     <t>Thats really good. You truly understand the factors and names. 
@@ -87,39 +67,49 @@
 The second sentence should describe the cluster’s specific strengths based on the available information.
 The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
 I will provided you with the cluster description and you will return the summary. 
-Here is the cluster description based on the factor scores at the cluster center, representing a typical football player in that cluster: ```Members of this cluster can be described as:  slightly low on good in air,  very low on goal-shy´´´</t>
-  </si>
-  <si>
-    <t>This cluster describes players who are prolific and consistent goal-scorers, although they exhibit a slight weakness in winning aerial duels.
-Their primary strength lies in their exceptional goal-scoring ability, consistently finding the back of the net and making every minute on the pitch count for scoring opportunities.
-However, they exhibit a slight weakness in aerial duels, meaning they are less likely to win contested balls in the air and may not be a significant threat from crosses or set pieces.</t>
-  </si>
-  <si>
-    <t>This cluster describes players who are exceptionally strong goal producers, while being average in their aerial abilities.
-Their primary strength lies in their prolific goal-scoring capability and consistent ability to generate high-quality scoring chances, regardless of playing time.
-A potential weakness is their average performance in aerial duels, meaning they are not particularly dominant when the ball is contested high in the air.</t>
-  </si>
-  <si>
-    <t>This cluster describes players who are generally not dominant in aerial duels and exhibit an average tendency to be goal-shy.
-Based on the provided factors, this cluster does not exhibit specific strengths in goal contribution or aerial ability.
-Their clear weaknesses include a marked inability to win aerial duels and a consistent lack of prolific scoring, meaning they are less impactful in situations requiring heading or regular goal production.</t>
-  </si>
-  <si>
-    <t>This cluster describes players who are exceptionally skilled at orchestrating attacks and creating chances, while maintaining a reliable, albeit not extraordinary, goal-scoring presence.
-Their paramount strength lies in their extraordinary capacity as a creative maestro, consistently dazzling with incisive passes, unlocking defenses, and winning crucial ground duels to drive their team's attack.
-However, while their goal-scoring is consistent, it remains at a normal level, indicating they are not exceptionally prolific in front of goal, especially when compared to their elite playmaking abilities.</t>
-  </si>
-  <si>
-    <t>This cluster represents players who are strong contributors to their team's attack, blending solid creative playmaking with a notable inclination to find the back of the net.
-Their specific strengths lie in their above-average ability to deliver dangerous passes, find crucial attacking space, and win ground duels, alongside a clear tendency to score goals and gain significant playing time.
-While highly effective, their creativity, though strong, doesn't reach the absolute pinnacle of a "maestro," suggesting they are consistently good but perhaps not always the most ingenious in every attacking phase.</t>
+Here is the cluster description based on the factor scores at the cluster center, representing a typical football player in that cluster: ```Members of this cluster can be described as:  slightly low on good in air,  very low on no scoring threat´´´</t>
+  </si>
+  <si>
+    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical football player in that cluster:  ```Members of this cluster can be described as:  normal on good in air,  quite high on scoring threat´´´</t>
+  </si>
+  <si>
+    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical football player in that cluster: ```Members of this cluster can be described as:  extremely high on creative maestro,  normal on scoring threat´´´</t>
+  </si>
+  <si>
+    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical football player in that cluster: ```Members of this cluster can be described as:  relatively low on good in air,  normal on no scoring threat´´´</t>
+  </si>
+  <si>
+    <t>Those were really good. Exactly what I am looking for. 
+Make sure you continue to use the same format and style in the next example. 
+I am now going to give you one last description task to complete. 
+You will receive information about the cluster based on the latent factors that best describe it.
+For each cluster, write a concise summary based on the available information.
+The first sentence should give an overview of the cluster. 
+The second sentence should describe the cluster’s specific strengths based on the available information.
+The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
+Now do the same thing with the following: ```Members of this cluster can be described as:  slightly high on creative maestro,  slightly low on no scoring threat´´´</t>
+  </si>
+  <si>
+    <t>This cluster describes players who are extremely potent goal-scorers, consistently finding the back of the net, although they exhibit a slight weakness in winning aerial duels. Their primary strength is their exceptional ability to be a scoring threat, consistently finding the back of the net and creating dangerous non-penalty scoring opportunities, often playing significant minutes on the field. However, their weakness lies in being slightly less effective at winning aerial duels, meaning they are not particularly dominant when the ball is contested high above the pitch.</t>
+  </si>
+  <si>
+    <t>This cluster identifies football players who are formidable threats in front of goal, consistently making an impact even if their aerial game is not their strongest asset. Their exceptional strength lies in their capacity to be a true goal-getter, regularly finding the back of the net and posing a significant danger for non-penalty scoring opportunities, often influencing matches without needing to play the full duration. However, their performance in aerial duels is only at a normal level, meaning they are not particularly dominant when the ball is contested high above the pitch.</t>
+  </si>
+  <si>
+    <t>This cluster describes players who are not particularly effective in winning aerial duels and who generally do not pose a significant threat in front of goal. Based on the provided factors, this cluster does not exhibit specific strengths in goal contribution or aerial ability. Their clear weaknesses include a marked inability to consistently win aerial duels and a general lack of significant goal-scoring presence or creation of dangerous offensive opportunities.</t>
+  </si>
+  <si>
+    <t>This cluster describes players who are exceptionally skilled at orchestrating attacks and creating chances, while maintaining a reliable, albeit not extraordinary, goal-scoring presence. Their paramount strength lies in their extraordinary capacity as a creative maestro, consistently dazzling with incisive passes, unlocking defenses, and winning crucial ground duels to drive their team's attack. However, while their goal-scoring is consistent, it remains at a normal level, indicating they are not exceptionally prolific in front of goal, especially when compared to their elite playmaking abilities.</t>
+  </si>
+  <si>
+    <t>This cluster represents players who are strong contributors to their team's attack, blending solid creative playmaking with a notable inclination to find the back of the net. Their specific strengths lie in their above-average ability to deliver dangerous passes, find crucial attacking space, and win ground duels, alongside a clear tendency to score goals and gain significant playing time. While highly effective, their creativity, though strong, doesn't reach the absolute pinnacle of a "maestro," suggesting they are consistently good but perhaps not always the most ingenious in every attacking phase.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,6 +121,12 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -176,7 +172,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -496,7 +492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="20" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -504,7 +500,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="40" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -512,47 +508,47 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="20" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="58" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>7</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="130" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="87" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="50" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="40" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" ht="50" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
@@ -560,9 +556,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" ht="100" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>19</v>

--- a/data/describe/few_shot/cluster/messages_foot.xlsx
+++ b/data/describe/few_shot/cluster/messages_foot.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\cluster\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{262B2E6A-87A5-40BC-B8A5-340B5C5C2322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDFB204D-D496-4919-A750-6058AD57C082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29685" yWindow="1560" windowWidth="22560" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="QandA_data" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>User</t>
   </si>
@@ -33,28 +33,37 @@
     <t>Assistant</t>
   </si>
   <si>
-    <t>What does it mean when a football player is described as good in air?</t>
-  </si>
-  <si>
-    <t>When a football player is described as 'good in air', it means they have a knack for winning aerial duels, often coming out on top when the ball is contested high above the pitch.</t>
-  </si>
-  <si>
-    <t>What does it mean when a football player is described as creative maestro?</t>
-  </si>
-  <si>
-    <t>A creative maestro is a player who constantly delivers dangerous passes in the attacking third, always finding space to receive the ball in crucial attacking positions, and threading ingenious smart passes while making crucial key passes. These players are also very strong in winning ground duels, demonstrating their ability to both create opportunities and fight for possession.</t>
-  </si>
-  <si>
-    <t>What does it mean when a football player is described as no scoring threat?</t>
-  </si>
-  <si>
-    <t>When a football player is described as "no scoring threat," it means they don't often find the back of the net or create many dangerous opportunities in front of goal. This also suggests they typically don't play extensive minutes on the field.</t>
-  </si>
-  <si>
-    <t>What does it mean when a football player is described as scoring threat?</t>
-  </si>
-  <si>
-    <t>A football player described as a 'scoring threat' is a true goal-getter, consistently finding the back of the net and posing a serious danger for non-penalty scoring opportunities. Their ability to score makes them a formidable presence on the field, and they don't necessarily need to play a full match to make an impact.</t>
+    <t>What does it mean when a football player is described as limited?</t>
+  </si>
+  <si>
+    <t>When a football player is described as limited, it suggests that their ability in certain aspects of the game may not be as impactful, particularly when it comes to air duels, which they might struggle with more than others. Essentially, they may not demonstrate the breadth of skills that allows them to influence the game significantly.</t>
+  </si>
+  <si>
+    <t>What does it mean when a football player is described as expansive?</t>
+  </si>
+  <si>
+    <t>When a football player is described as expansive, it means they are highly engaged in the game, demonstrating their ability to make impactful plays. With a knack for delivering smart passes, winning ground duels, and making key contributions in the final third, an expansive player is dynamic and influential on the pitch, showcasing their skills in creating opportunities and keeping the flow of the game alive.</t>
+  </si>
+  <si>
+    <t>What does it mean when a football player is described as not scoring?</t>
+  </si>
+  <si>
+    <t>When a football player is described as not scoring, it indicates a lack of contributions to the team's goal tally. Unlike players who showcase their ability by frequently finding the back of the net, those labeled as not scoring fail to register goals or impactful chances, which means they might be less involved in crucial scoring situations during the game.</t>
+  </si>
+  <si>
+    <t>What does it mean when a football player is described as scoring?</t>
+  </si>
+  <si>
+    <t>When a football player is described as scoring, it means they have a knack for finding the back of the net, showcasing their ability to score goals consistently. This is highlighted by their impressive goals adjusted per 90 minutes and their non-penalty expected goals, making them a key player on the field who contributes significantly to their team's success.</t>
+  </si>
+  <si>
+    <t>This cluster is characterized by football players who are relatively agile and able to contribute effectively to the game. Their specific strength lies in their scoring ability, indicating they can consistently find the back of the net when opportunities arise. However, the slightly low score on being limited suggests they may not excel in certain areas of their skill set, which could potentially hinder their overall versatility on the field.</t>
+  </si>
+  <si>
+    <t>This cluster consists of football players who are characterized by their expansive playing style and greater ability to score. Their specific strength lies in their ability to create opportunities on the field, showcasing creativity and versatility in their gameplay. However, the cluster may lack players who are more limited in specific roles, potentially impacting specialized play when necessary.</t>
+  </si>
+  <si>
+    <t>This cluster comprises football players who demonstrate an average level of limitations in their gameplay while showing a relatively low incidence of failing to score. The primary strength of this cluster lies in their consistent ability to contribute to the game, as they are less likely to go without scoring opportunities. Conversely, their normal level of limitations suggests that they may not excel in high-impact skills that could elevate their overall performance.</t>
   </si>
   <si>
     <t>Thats really good. You truly understand the factors and names. 
@@ -67,16 +76,10 @@
 The second sentence should describe the cluster’s specific strengths based on the available information.
 The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
 I will provided you with the cluster description and you will return the summary. 
-Here is the cluster description based on the factor scores at the cluster center, representing a typical football player in that cluster: ```Members of this cluster can be described as:  slightly low on good in air,  very low on no scoring threat´´´</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical football player in that cluster:  ```Members of this cluster can be described as:  normal on good in air,  quite high on scoring threat´´´</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical football player in that cluster: ```Members of this cluster can be described as:  extremely high on creative maestro,  normal on scoring threat´´´</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical football player in that cluster: ```Members of this cluster can be described as:  relatively low on good in air,  normal on no scoring threat´´´</t>
+Here is the cluster description based on the factor scores at the cluster center, representing a typical football player in that cluster: ```Members of this cluster can be described as:  slightly low on limited,  quite high on scoring´´´</t>
+  </si>
+  <si>
+    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical football player in that cluster:  ``Members of this cluster can be described as:  extremely high on expansive,  slightly high on scoring`´´´</t>
   </si>
   <si>
     <t>Those were really good. Exactly what I am looking for. 
@@ -87,29 +90,14 @@
 The first sentence should give an overview of the cluster. 
 The second sentence should describe the cluster’s specific strengths based on the available information.
 The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
-Now do the same thing with the following: ```Members of this cluster can be described as:  slightly high on creative maestro,  slightly low on no scoring threat´´´</t>
-  </si>
-  <si>
-    <t>This cluster describes players who are extremely potent goal-scorers, consistently finding the back of the net, although they exhibit a slight weakness in winning aerial duels. Their primary strength is their exceptional ability to be a scoring threat, consistently finding the back of the net and creating dangerous non-penalty scoring opportunities, often playing significant minutes on the field. However, their weakness lies in being slightly less effective at winning aerial duels, meaning they are not particularly dominant when the ball is contested high above the pitch.</t>
-  </si>
-  <si>
-    <t>This cluster identifies football players who are formidable threats in front of goal, consistently making an impact even if their aerial game is not their strongest asset. Their exceptional strength lies in their capacity to be a true goal-getter, regularly finding the back of the net and posing a significant danger for non-penalty scoring opportunities, often influencing matches without needing to play the full duration. However, their performance in aerial duels is only at a normal level, meaning they are not particularly dominant when the ball is contested high above the pitch.</t>
-  </si>
-  <si>
-    <t>This cluster describes players who are not particularly effective in winning aerial duels and who generally do not pose a significant threat in front of goal. Based on the provided factors, this cluster does not exhibit specific strengths in goal contribution or aerial ability. Their clear weaknesses include a marked inability to consistently win aerial duels and a general lack of significant goal-scoring presence or creation of dangerous offensive opportunities.</t>
-  </si>
-  <si>
-    <t>This cluster describes players who are exceptionally skilled at orchestrating attacks and creating chances, while maintaining a reliable, albeit not extraordinary, goal-scoring presence. Their paramount strength lies in their extraordinary capacity as a creative maestro, consistently dazzling with incisive passes, unlocking defenses, and winning crucial ground duels to drive their team's attack. However, while their goal-scoring is consistent, it remains at a normal level, indicating they are not exceptionally prolific in front of goal, especially when compared to their elite playmaking abilities.</t>
-  </si>
-  <si>
-    <t>This cluster represents players who are strong contributors to their team's attack, blending solid creative playmaking with a notable inclination to find the back of the net. Their specific strengths lie in their above-average ability to deliver dangerous passes, find crucial attacking space, and win ground duels, alongside a clear tendency to score goals and gain significant playing time. While highly effective, their creativity, though strong, doesn't reach the absolute pinnacle of a "maestro," suggesting they are consistently good but perhaps not always the most ingenious in every attacking phase.</t>
+Now do the same thing with the following, here is the cluster description based on the factor scores at the cluster center, representing a typical football player in that cluster:  ```Members of this cluster can be described as:  normal on limited,  relatively low on not scoring´´´</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -118,9 +106,138 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
@@ -129,15 +246,188 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -146,41 +436,215 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -203,44 +667,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -267,14 +731,32 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -301,6 +783,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -312,176 +812,152 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="94.26953125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="78.7265625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="83.54296875" customWidth="1"/>
+    <col min="2" max="2" width="79.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -492,80 +968,64 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:2" ht="52" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="40" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:2" ht="65" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="20" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:2" ht="52" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:2" ht="52" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="130" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3" t="s">
+    </row>
+    <row r="7" spans="1:2" ht="40" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="110" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="50" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="40" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="B8" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="50" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="100" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/describe/few_shot/cluster/messages_foot.xlsx
+++ b/data/describe/few_shot/cluster/messages_foot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\cluster\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDFB204D-D496-4919-A750-6058AD57C082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55130725-C5F6-4A36-AF2C-04AD41F0BCF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,15 +57,6 @@
     <t>When a football player is described as scoring, it means they have a knack for finding the back of the net, showcasing their ability to score goals consistently. This is highlighted by their impressive goals adjusted per 90 minutes and their non-penalty expected goals, making them a key player on the field who contributes significantly to their team's success.</t>
   </si>
   <si>
-    <t>This cluster is characterized by football players who are relatively agile and able to contribute effectively to the game. Their specific strength lies in their scoring ability, indicating they can consistently find the back of the net when opportunities arise. However, the slightly low score on being limited suggests they may not excel in certain areas of their skill set, which could potentially hinder their overall versatility on the field.</t>
-  </si>
-  <si>
-    <t>This cluster consists of football players who are characterized by their expansive playing style and greater ability to score. Their specific strength lies in their ability to create opportunities on the field, showcasing creativity and versatility in their gameplay. However, the cluster may lack players who are more limited in specific roles, potentially impacting specialized play when necessary.</t>
-  </si>
-  <si>
-    <t>This cluster comprises football players who demonstrate an average level of limitations in their gameplay while showing a relatively low incidence of failing to score. The primary strength of this cluster lies in their consistent ability to contribute to the game, as they are less likely to go without scoring opportunities. Conversely, their normal level of limitations suggests that they may not excel in high-impact skills that could elevate their overall performance.</t>
-  </si>
-  <si>
     <t>Thats really good. You truly understand the factors and names. 
 Now your task is to provide a description of a cluster.
 Please use the statistical description enclosed with ``` ´´´ . It provides information about the cluster based on the latent factors that most accurately describe it.
@@ -91,6 +82,15 @@
 The second sentence should describe the cluster’s specific strengths based on the available information.
 The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
 Now do the same thing with the following, here is the cluster description based on the factor scores at the cluster center, representing a typical football player in that cluster:  ```Members of this cluster can be described as:  normal on limited,  relatively low on not scoring´´´</t>
+  </si>
+  <si>
+    <t>These players are specialized in offensive threats who prioritize clinical efficiency over a broad tactical range. Their primary strength is an elite scoring instinct, evidenced by their consistent ability to find the back of the net and contribute high non-penalty expected goals per 90 minutes. However, their profile suggests a lack of versatility, as they may struggle to influence the wider game or compete effectively in areas like aerial duels.</t>
+  </si>
+  <si>
+    <t>These players are dynamic and highly influential playmakers who dominate the pitch with an all-action style of play. Their primary strengths lie in their ability to orchestrate the game through smart passing and ground duels, while simultaneously maintaining a consistent threat in front of goal. Because they rank so highly across expansive and scoring metrics, they exhibit virtually no significant weaknesses, showcasing a versatile skill set that keeps the flow of the game alive.</t>
+  </si>
+  <si>
+    <t>They are reliable players who maintain a standard presence on the pitch without leaning into extreme roles. Their specific strength is their consistent contribution to the team's offensive output, as being low on "not scoring" indicates they frequently find the back of the net or create impactful chances. However, their average rating for "limited" suggests they may occasionally lack the breadth of skills needed to exert a dominant influence over the entire game, particularly in specialized areas like aerial duels.</t>
   </si>
 </sst>
 </file>
@@ -1002,26 +1002,26 @@
     </row>
     <row r="6" spans="1:2" ht="130" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="40" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="110" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data/describe/few_shot/cluster/messages_foot.xlsx
+++ b/data/describe/few_shot/cluster/messages_foot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\cluster\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55130725-C5F6-4A36-AF2C-04AD41F0BCF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C09C045A-BBDC-4D82-9B6C-0CF75775814A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>User</t>
   </si>
@@ -33,71 +33,47 @@
     <t>Assistant</t>
   </si>
   <si>
-    <t>What does it mean when a football player is described as limited?</t>
-  </si>
-  <si>
-    <t>When a football player is described as limited, it suggests that their ability in certain aspects of the game may not be as impactful, particularly when it comes to air duels, which they might struggle with more than others. Essentially, they may not demonstrate the breadth of skills that allows them to influence the game significantly.</t>
-  </si>
-  <si>
-    <t>What does it mean when a football player is described as expansive?</t>
-  </si>
-  <si>
-    <t>When a football player is described as expansive, it means they are highly engaged in the game, demonstrating their ability to make impactful plays. With a knack for delivering smart passes, winning ground duels, and making key contributions in the final third, an expansive player is dynamic and influential on the pitch, showcasing their skills in creating opportunities and keeping the flow of the game alive.</t>
-  </si>
-  <si>
-    <t>What does it mean when a football player is described as not scoring?</t>
-  </si>
-  <si>
-    <t>When a football player is described as not scoring, it indicates a lack of contributions to the team's goal tally. Unlike players who showcase their ability by frequently finding the back of the net, those labeled as not scoring fail to register goals or impactful chances, which means they might be less involved in crucial scoring situations during the game.</t>
+    <t>What does it mean when a football player is described as defensive?</t>
+  </si>
+  <si>
+    <t>When a football player is described as defensive, it suggests that they are not particularly focused on winning aerial duels, as this feature is weakly associated with being defensive. Instead, their playstyle leans more towards containing and protecting rather than initiating creative offensive plays.</t>
+  </si>
+  <si>
+    <t>What does it mean when a football player is described as creative?</t>
+  </si>
+  <si>
+    <t>A creative player is a true architect on the field, constantly delivering crucial passes into the final third and receiving the ball in dangerous areas, often executing clever and key passes that unlock defenses. They are also adept at winning ground duels, showcasing their ability to not only create but also maintain possession and drive forward.</t>
+  </si>
+  <si>
+    <t>What does it mean when a football player is described as not passive?</t>
+  </si>
+  <si>
+    <t>When a football player is described as not passive, it means they are not simply waiting for the game to come to them; instead, they are actively engaged in making plays and contributing to the team's performance. This player is likely to take initiative, demonstrating their fierce competitive spirit and drive to impact the game, even if specific features are not directly associated with this trait.</t>
   </si>
   <si>
     <t>What does it mean when a football player is described as scoring?</t>
   </si>
   <si>
-    <t>When a football player is described as scoring, it means they have a knack for finding the back of the net, showcasing their ability to score goals consistently. This is highlighted by their impressive goals adjusted per 90 minutes and their non-penalty expected goals, making them a key player on the field who contributes significantly to their team's success.</t>
-  </si>
-  <si>
-    <t>Thats really good. You truly understand the factors and names. 
-Now your task is to provide a description of a cluster.
-Please use the statistical description enclosed with ``` ´´´ . It provides information about the cluster based on the latent factors that most accurately describe it.
-Now your task is to provide a description of a cluster.
-You will receive information about the cluster based on the latent factors that best describe it.
-For each cluster, write a concise summary based on the available information.
-The first sentence should give an overview of the cluster. 
-The second sentence should describe the cluster’s specific strengths based on the available information.
-The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
-I will provided you with the cluster description and you will return the summary. 
-Here is the cluster description based on the factor scores at the cluster center, representing a typical football player in that cluster: ```Members of this cluster can be described as:  slightly low on limited,  quite high on scoring´´´</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical football player in that cluster:  ``Members of this cluster can be described as:  extremely high on expansive,  slightly high on scoring`´´´</t>
-  </si>
-  <si>
-    <t>Those were really good. Exactly what I am looking for. 
-Make sure you continue to use the same format and style in the next example. 
-I am now going to give you one last description task to complete. 
-You will receive information about the cluster based on the latent factors that best describe it.
-For each cluster, write a concise summary based on the available information.
-The first sentence should give an overview of the cluster. 
-The second sentence should describe the cluster’s specific strengths based on the available information.
-The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
-Now do the same thing with the following, here is the cluster description based on the factor scores at the cluster center, representing a typical football player in that cluster:  ```Members of this cluster can be described as:  normal on limited,  relatively low on not scoring´´´</t>
-  </si>
-  <si>
-    <t>These players are specialized in offensive threats who prioritize clinical efficiency over a broad tactical range. Their primary strength is an elite scoring instinct, evidenced by their consistent ability to find the back of the net and contribute high non-penalty expected goals per 90 minutes. However, their profile suggests a lack of versatility, as they may struggle to influence the wider game or compete effectively in areas like aerial duels.</t>
-  </si>
-  <si>
-    <t>These players are dynamic and highly influential playmakers who dominate the pitch with an all-action style of play. Their primary strengths lie in their ability to orchestrate the game through smart passing and ground duels, while simultaneously maintaining a consistent threat in front of goal. Because they rank so highly across expansive and scoring metrics, they exhibit virtually no significant weaknesses, showcasing a versatile skill set that keeps the flow of the game alive.</t>
-  </si>
-  <si>
-    <t>They are reliable players who maintain a standard presence on the pitch without leaning into extreme roles. Their specific strength is their consistent contribution to the team's offensive output, as being low on "not scoring" indicates they frequently find the back of the net or create impactful chances. However, their average rating for "limited" suggests they may occasionally lack the breadth of skills needed to exert a dominant influence over the entire game, particularly in specialized areas like aerial duels.</t>
+    <t>When a football player is described as scoring, it means they are highly effective in finding the back of the net, with a strong focus on goals adjusted per 90 minutes and non-penalty expected goals adjusted over the same timeframe. This player's ability to convert chances into goals is what sets them apart, while their time on the pitch plays a lesser role in defining their scoring prowess.</t>
+  </si>
+  <si>
+    <t>From your answers I see that you have all the information you need about the factors. We are now going to do the most important task: provide a description of a cluster. Make sure you continue to use the same format and style as in earlier examples. This is the last description task to complete, so please pay close attention. You will receive information about the cluster based on the latent factors that best describe it. For each cluster, write a concise summary based on the available information. The first sentence should give an overview of the cluster. The second sentence should describe the cluster’s specific strengths based on the available information, if any exists. The third sentence should describe the cluster’s specific weaknesses based on the available information, if any exists. Now do this task based on the following description: ```Members of this cluster can be described as: slightly low on defensive, very low on not passive´´´</t>
+  </si>
+  <si>
+    <t>These football players exhibit a tendency towards less defensive play and a significant propensity to be passive. Their strength lies in their openness to creative play, allowing them the potential to engage in dynamic offensive strategies. However, their notable passivity might hinder their effectiveness in proactive defense and assertiveness on the field.</t>
+  </si>
+  <si>
+    <t>These players are generally balanced in their defensive capabilities while demonstrating a strong aptitude for scoring. Their ability to find the back of the net signifies a compelling offensive presence, making them valuable assets on the field. However, their normal level of defensiveness may indicate a need for improvement in guarding against opponents and contributing to the defensive strategy.</t>
+  </si>
+  <si>
+    <t>Now do this task based on the following description: ```Members of this cluster can be described as: normal on defensive, quite high on scoring´´´</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -231,19 +207,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -587,15 +550,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -953,76 +910,96 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="83.54296875" customWidth="1"/>
-    <col min="2" max="2" width="79.08984375" customWidth="1"/>
+    <col min="1" max="1" width="61.6328125" customWidth="1"/>
+    <col min="2" max="2" width="82.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="52" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="65" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="52" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="52" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="130" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:2" ht="203" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="40" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="110" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+      <c r="B7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>15</v>
-      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
